--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D534B2-7A0E-47FC-89AE-A8210A202E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FDD7D9-5A5F-4251-A6B2-A35FD4E3EB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2-shot" sheetId="1" r:id="rId1"/>
+    <sheet name="OG" sheetId="1" r:id="rId1"/>
+    <sheet name="Better Parsing" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="26">
   <si>
     <t>human1</t>
   </si>
@@ -96,6 +97,24 @@
   </si>
   <si>
     <t>Total prompts</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (two-shot) without texts 1, 5, 7, 43</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (three-shot) without texts  1, 5, 7, 43</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (four-shot) without texts  1, 5, 7, 43</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (zero-shot) without texts  1, 5, 7, 43</t>
+  </si>
+  <si>
+    <t>Statistics of TOTALLY unparsable JSONs, that were skipped</t>
+  </si>
+  <si>
+    <t>Amount of individual skipped questions</t>
   </si>
 </sst>
 </file>
@@ -127,7 +146,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -200,11 +219,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -214,9 +242,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -226,14 +251,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -552,23 +606,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="12"/>
-      <c r="I1" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="12"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="11"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -734,23 +788,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="I8" s="10" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="I8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="11"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -916,23 +970,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="I15" s="10" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+      <c r="I15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="11"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1111,22 +1165,22 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="I25" s="9" t="s">
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="9"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -1331,10 +1385,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23 G29:G1048576">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1376,4 +1430,738 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB0AADD-8776-4402-85B4-2B481E8BF56B}">
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
+      <c r="I1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="11"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.85926928281461401</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.94494047619047605</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.90007087172218203</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.86890770283462404</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.73877176901924801</v>
+      </c>
+      <c r="G3" s="6">
+        <f>E3-M3</f>
+        <v>2.2674654906410519E-3</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.86164383561643798</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.93601190476190399</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0.897289586305278</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0.86664023734398299</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.73400738868364701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.66949152542372803</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.90285714285714203</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.76885644768856398</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.74832507198181797</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.50937754824680603</v>
+      </c>
+      <c r="G4" s="6">
+        <f>E4-M4</f>
+        <v>-4.4219885565159878E-3</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.66849315068493098</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.92952380952380897</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.777689243027888</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.75274706053833396</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.52113821138211303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.88219544846050801</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.89295392953929498</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.88754208754208697</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.838739597230163</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.67750132129934504</v>
+      </c>
+      <c r="G5" s="6">
+        <f>E5-M5</f>
+        <v>8.9722115574879524E-3</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.88356164383561597</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.87398373983739797</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.87874659400544897</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0.82976738567267505</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.65955305013086296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.86516853932584203</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.89017341040462405</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.86026527663088304</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.72089067573836396</v>
+      </c>
+      <c r="G10" s="6">
+        <f>E10-M3</f>
+        <v>-6.374960713099953E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0.66430594900849804</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.89333333333333298</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.76198212835093404</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.74133424816021398</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.49546855174913801</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" ref="G11:G12" si="0">E11-M4</f>
+        <v>-1.1412812378119974E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0.88423988842398804</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.85907859078590698</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.87147766323024001</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.822405498281787</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.644941439820921</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="0"/>
+        <v>-7.3618873908880555E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.85574229691876702</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.90922619047619002</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.88167388167388105</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.84911434575864098</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.69865769215891005</v>
+      </c>
+      <c r="G17" s="6">
+        <f>E17-M3</f>
+        <v>-1.7525891585342013E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.66911764705882304</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.86666666666666603</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.755186721991701</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.74038405867026902</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0.49022282855843502</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" ref="G18:G19" si="1">E18-M4</f>
+        <v>-1.2363001868064938E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0.878284923928077</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.86043360433604299</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.86926762491444198</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.81802819585160402</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.63612481450286695</v>
+      </c>
+      <c r="G19" s="6">
+        <f t="shared" si="1"/>
+        <v>-1.1739189821071028E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="6">
+        <f>B26/$J$26</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>8</v>
+      </c>
+      <c r="E26" s="6">
+        <f>D26/$J$27</f>
+        <v>0.04</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6</v>
+      </c>
+      <c r="G26" s="6">
+        <f>F26/$J$28</f>
+        <v>0.03</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <v>9</v>
+      </c>
+      <c r="C27" s="6">
+        <f>B27/$J$26</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>6</v>
+      </c>
+      <c r="E27" s="6">
+        <f>D27/$J$27</f>
+        <v>0.03</v>
+      </c>
+      <c r="F27" s="2">
+        <v>8</v>
+      </c>
+      <c r="G27" s="6">
+        <f>F27/$J$28</f>
+        <v>0.04</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2</v>
+      </c>
+      <c r="C28" s="6">
+        <f>B28/$J$26</f>
+        <v>0.01</v>
+      </c>
+      <c r="D28" s="2">
+        <v>8</v>
+      </c>
+      <c r="E28" s="6">
+        <f>D28/$J$27</f>
+        <v>0.04</v>
+      </c>
+      <c r="F28" s="2">
+        <v>4</v>
+      </c>
+      <c r="G28" s="6">
+        <f>F28/$J$28</f>
+        <v>0.02</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="17">
+        <v>2</v>
+      </c>
+      <c r="C32" s="17">
+        <v>9</v>
+      </c>
+      <c r="D32" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0</v>
+      </c>
+      <c r="C33" s="17">
+        <v>4</v>
+      </c>
+      <c r="D33" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="17">
+        <v>0</v>
+      </c>
+      <c r="C34" s="17">
+        <v>4</v>
+      </c>
+      <c r="D34" s="17">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B2:G2">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:G9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:G16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G23">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:N2">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FDD7D9-5A5F-4251-A6B2-A35FD4E3EB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D38587-311C-4D5D-A227-9ACDD9A49825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OG" sheetId="1" r:id="rId1"/>
     <sheet name="Better Parsing" sheetId="2" r:id="rId2"/>
+    <sheet name="Json-repair" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="26">
   <si>
     <t>human1</t>
   </si>
@@ -232,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -242,6 +243,17 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -251,23 +263,101 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -606,23 +696,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="11"/>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -788,23 +878,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="I8" s="9" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="I8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -970,23 +1060,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="I15" s="9" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="I15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="11"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1385,10 +1475,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23 G29:G1048576">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1451,23 +1541,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="11"/>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1647,15 +1737,15 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1765,15 +1855,15 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -2026,28 +2116,28 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2055,13 +2145,13 @@
       <c r="A32" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="2">
         <v>2</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="2">
         <v>9</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="2">
         <v>25</v>
       </c>
     </row>
@@ -2069,13 +2159,13 @@
       <c r="A33" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
-      <c r="C33" s="17">
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="2">
         <v>4</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="2">
         <v>20</v>
       </c>
     </row>
@@ -2083,28 +2173,28 @@
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
-      <c r="C34" s="17">
+      <c r="B34" s="2">
+        <v>0</v>
+      </c>
+      <c r="C34" s="2">
         <v>4</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="2">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="7">
@@ -2143,10 +2233,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2164,4 +2254,638 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762865AC-13CA-4EC7-88AB-2DFC0996DA3B}">
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6">
+        <f>E3-M3</f>
+        <v>-0.86664023734398299</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.86164383561643798</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0.93601190476190399</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0.897289586305278</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0.86664023734398299</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0.73400738868364701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6">
+        <f>E4-M4</f>
+        <v>-0.75274706053833396</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.66849315068493098</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0.92952380952380897</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.777689243027888</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.75274706053833396</v>
+      </c>
+      <c r="N4" s="6">
+        <v>0.52113821138211303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6">
+        <f>E5-M5</f>
+        <v>-0.82976738567267505</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0.88356164383561597</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0.87398373983739797</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.87874659400544897</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0.82976738567267505</v>
+      </c>
+      <c r="N5" s="6">
+        <v>0.65955305013086296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6">
+        <f>E10-M3</f>
+        <v>-0.86664023734398299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6">
+        <f t="shared" ref="G11:G12" si="0">E11-M4</f>
+        <v>-0.75274706053833396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6">
+        <f t="shared" si="0"/>
+        <v>-0.82976738567267505</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6">
+        <f>E17-M3</f>
+        <v>-0.86664023734398299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6">
+        <f t="shared" ref="G18:G19" si="1">E18-M4</f>
+        <v>-0.75274706053833396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.82976738567267505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6">
+        <f>B26/$J$26</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <f>D26/$J$27</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <f>F26/$J$28</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6">
+        <f>B27/$J$26</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <f>D27/$J$27</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <f>F27/$J$28</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6">
+        <f>B28/$J$26</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <f>D28/$J$27</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <f>F28/$J$28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B2:G2">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:G9">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:G16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G23">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:N2">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:G28">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D38587-311C-4D5D-A227-9ACDD9A49825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7527E765-3EA9-4965-B543-312022DE119A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="29">
   <si>
     <t>human1</t>
   </si>
@@ -116,6 +116,15 @@
   </si>
   <si>
     <t>Amount of individual skipped questions</t>
+  </si>
+  <si>
+    <t>Amount of individual skipped invalid JSON objects</t>
+  </si>
+  <si>
+    <t>Amount of times when had to insert default complies=False except those on top</t>
+  </si>
+  <si>
+    <t>Total questions. NB! Approx, because for some texts 1 question in Goal and Tasks might be ommited</t>
   </si>
 </sst>
 </file>
@@ -233,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -248,12 +257,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -263,21 +266,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -300,16 +312,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -325,36 +327,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -696,23 +668,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-      <c r="I1" s="14" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="16"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -878,23 +850,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="I8" s="14" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
+      <c r="I8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1060,23 +1032,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="I15" s="14" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
+      <c r="I15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="16"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1242,35 +1214,35 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="16"/>
+      <c r="F25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="16"/>
+      <c r="I25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -1475,10 +1447,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23 G29:G1048576">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1541,23 +1513,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-      <c r="I1" s="14" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="I1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="16"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1737,15 +1709,15 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1855,15 +1827,15 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1987,37 +1959,37 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="16"/>
+      <c r="F25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="16"/>
+      <c r="I25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -2185,16 +2157,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I25:J25"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="7">
@@ -2233,10 +2205,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2258,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762865AC-13CA-4EC7-88AB-2DFC0996DA3B}">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
@@ -2275,23 +2247,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-      <c r="I1" s="14" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="I1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="16"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2331,17 +2303,27 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="A3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.85885486018641799</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.95982142857142805</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.90653548840477804</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.87567147815804802</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.75260901063184005</v>
+      </c>
       <c r="G3" s="6">
         <f>E3-M3</f>
-        <v>-0.86664023734398299</v>
+        <v>9.0312408140650335E-3</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>0</v>
@@ -2363,17 +2345,27 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="6">
+        <v>0.66352624495289303</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.93904761904761902</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.77760252365930604</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.749473198588546</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.51684025429460301</v>
+      </c>
       <c r="G4" s="6">
         <f>E4-M4</f>
-        <v>-0.75274706053833396</v>
+        <v>-3.2738619497879595E-3</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>1</v>
@@ -2395,17 +2387,27 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="B5" s="6">
+        <v>0.88297872340425498</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.89972899728997202</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.89127516778523397</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.84310593832299696</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.68626411709544499</v>
+      </c>
       <c r="G5" s="6">
         <f>E5-M5</f>
-        <v>-0.82976738567267505</v>
+        <v>1.3338552650321911E-2</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>2</v>
@@ -2427,32 +2429,36 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
@@ -2473,74 +2479,108 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.86118598382749301</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.95089285714285698</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.90381895332390305</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.87338753670814095</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.74778432827079999</v>
+      </c>
       <c r="G10" s="6">
         <f>E10-M3</f>
-        <v>-0.86664023734398299</v>
+        <v>6.7472993641579659E-3</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="B11" s="6">
+        <v>0.66392318244170101</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.92190476190476101</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.77192982456140302</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.74658869395711402</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.50905723449428497</v>
+      </c>
       <c r="G11" s="6">
         <f t="shared" ref="G11:G12" si="0">E11-M4</f>
-        <v>-0.75274706053833396</v>
+        <v>-6.1583665812199317E-3</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="B12" s="6">
+        <v>0.88651535380507296</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.89972899728997202</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.89307330195023504</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.84628444416553295</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.69260043143799099</v>
+      </c>
       <c r="G12" s="6">
         <f t="shared" si="0"/>
-        <v>-0.82976738567267505</v>
+        <v>1.6517058492857895E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
@@ -2561,45 +2601,75 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.85365853658536495</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.89361702127659504</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.86060161408657299</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.72218972979295804</v>
+      </c>
       <c r="G17" s="6">
         <f>E17-M3</f>
-        <v>-0.86664023734398299</v>
+        <v>-6.0386232574100029E-3</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="B18" s="6">
+        <v>0.66524822695035402</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.89333333333333298</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.76260162601626003</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.74225319396051104</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0.49712213913437497</v>
+      </c>
       <c r="G18" s="6">
         <f t="shared" ref="G18:G19" si="1">E18-M4</f>
-        <v>-0.75274706053833396</v>
+        <v>-1.0493866577822919E-2</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="6">
+        <v>0.87956698240866005</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.88075880758807501</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.88016249153689896</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.82986953966633203</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.65973936622283302</v>
+      </c>
       <c r="G19" s="6">
         <f t="shared" si="1"/>
-        <v>-0.82976738567267505</v>
+        <v>1.0215399365698374E-4</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2631,37 +2701,37 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="16"/>
+      <c r="F25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="16"/>
+      <c r="I25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -2761,7 +2831,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2770,8 +2840,10 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="I30" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
@@ -2784,33 +2856,136 @@
       <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="I31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="2">
+        <f>64*19</f>
+        <v>1216</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2">
+        <v>26</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="2">
+        <f t="shared" ref="J32:J33" si="2">64*19</f>
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="2">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <v>20</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" si="2"/>
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
@@ -2858,11 +3033,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="B26:G28">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G23">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2878,14 +3061,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:G28">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7527E765-3EA9-4965-B543-312022DE119A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF89596-C151-4CE9-996A-1D59E24D8C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="30">
   <si>
     <t>human1</t>
   </si>
@@ -124,7 +124,10 @@
     <t>Amount of times when had to insert default complies=False except those on top</t>
   </si>
   <si>
-    <t>Total questions. NB! Approx, because for some texts 1 question in Goal and Tasks might be ommited</t>
+    <t>Total percentage of unanswered questions</t>
+  </si>
+  <si>
+    <t>Total questions</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -254,6 +257,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,13 +276,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -282,14 +285,281 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -668,23 +938,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="I1" s="12" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="14"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -850,23 +1120,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-      <c r="I8" s="12" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
+      <c r="I8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="14"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1032,23 +1302,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="I15" s="12" t="s">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="I15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1214,35 +1484,35 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16" t="s">
+      <c r="E25" s="13"/>
+      <c r="F25" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="I25" s="16" t="s">
+      <c r="G25" s="13"/>
+      <c r="I25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="16"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -1447,10 +1717,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23 G29:G1048576">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1513,23 +1783,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="I1" s="12" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="14"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1709,15 +1979,15 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1827,15 +2097,15 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1959,37 +2229,37 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16" t="s">
+      <c r="E25" s="13"/>
+      <c r="F25" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="I25" s="16" t="s">
+      <c r="G25" s="13"/>
+      <c r="I25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="16"/>
+      <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -2088,12 +2358,12 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -2157,16 +2427,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="7">
@@ -2205,10 +2475,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2238,7 +2508,9 @@
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" customWidth="1"/>
     <col min="10" max="10" width="17.140625" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" customWidth="1"/>
@@ -2247,23 +2519,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="I1" s="12" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="14"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2303,7 +2575,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6">
@@ -2479,7 +2751,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="6">
@@ -2600,8 +2872,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B17" s="6">
@@ -2624,7 +2896,7 @@
         <v>-6.0386232574100029E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
@@ -2648,7 +2920,7 @@
         <v>-1.0493866577822919E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
@@ -2672,68 +2944,72 @@
         <v>1.0215399365698374E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16" t="s">
+      <c r="E25" s="13"/>
+      <c r="F25" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="I25" s="16" t="s">
+      <c r="G25" s="13"/>
+      <c r="I25" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="13"/>
+      <c r="L25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>0</v>
       </c>
@@ -2764,8 +3040,14 @@
       <c r="J26" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M26" s="2">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>1</v>
       </c>
@@ -2796,8 +3078,14 @@
       <c r="J27" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" s="2">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>2</v>
       </c>
@@ -2828,24 +3116,26 @@
       <c r="J28" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="L28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" s="2">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="16"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="10" t="s">
         <v>16</v>
@@ -2856,15 +3146,14 @@
       <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="2">
-        <f>64*19</f>
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F31" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>0</v>
       </c>
@@ -2877,15 +3166,18 @@
       <c r="D32" s="2">
         <v>26</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="F32" s="2"/>
+      <c r="G32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J32" s="2">
-        <f t="shared" ref="J32:J33" si="2">64*19</f>
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>1</v>
       </c>
@@ -2898,15 +3190,23 @@
       <c r="D33" s="2">
         <v>20</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="2">
-        <f t="shared" si="2"/>
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F33" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
+        <f>(B32+B37)/M26</f>
+        <v>3.0674846625766872E-3</v>
+      </c>
+      <c r="H33" s="6">
+        <f>(C32+C37)/M26</f>
+        <v>1.0224948875255624E-2</v>
+      </c>
+      <c r="I33" s="6">
+        <f>(D32+D37)/M26</f>
+        <v>2.8629856850715747E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
@@ -2919,16 +3219,46 @@
       <c r="D34" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="F34" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" ref="G34:G35" si="2">(B33+B38)/M27</f>
+        <v>1.0224948875255625E-3</v>
+      </c>
+      <c r="H34" s="6">
+        <f t="shared" ref="H34:H35" si="3">(C33+C38)/M27</f>
+        <v>6.1349693251533744E-3</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" ref="I34:I35" si="4">(D33+D38)/M27</f>
+        <v>2.1472392638036811E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="F35" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="2"/>
+        <v>2.0449897750511249E-3</v>
+      </c>
+      <c r="H35" s="6">
+        <f t="shared" si="3"/>
+        <v>9.202453987730062E-3</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="4"/>
+        <v>2.4539877300613498E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="10" t="s">
         <v>16</v>
@@ -2940,7 +3270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>0</v>
       </c>
@@ -2954,7 +3284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>1</v>
       </c>
@@ -2968,7 +3298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>2</v>
       </c>
@@ -2983,21 +3313,46 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="L25:M25"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A24:J24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:G9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:G16">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3009,8 +3364,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:G9">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="B26:G28">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G23">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:N2">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3021,44 +3392,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:G16">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+  <conditionalFormatting sqref="G33:I35">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+      <formula>1</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:G28">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:N2">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+      <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF89596-C151-4CE9-996A-1D59E24D8C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DEF4BF-079E-454D-8AFF-7E1ABCF466A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="31">
   <si>
     <t>human1</t>
   </si>
@@ -129,12 +129,15 @@
   <si>
     <t>Total questions</t>
   </si>
+  <si>
+    <t>F1 makro diff</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +153,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -242,8 +269,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -258,11 +287,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,18 +320,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -337,226 +386,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -938,23 +767,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
-      <c r="I1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1120,23 +949,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="I8" s="15" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+      <c r="I8" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="18"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1302,23 +1131,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
-      <c r="I15" s="15" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+      <c r="I15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="18"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1484,35 +1313,35 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="I25" s="13" t="s">
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="13"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -1717,10 +1546,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23 G29:G1048576">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1783,23 +1612,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
-      <c r="I1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="I1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1979,15 +1808,15 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -2097,15 +1926,15 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -2229,37 +2058,37 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="I25" s="13" t="s">
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="13"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -2358,12 +2187,12 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -2427,16 +2256,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I25:J25"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="7">
@@ -2475,10 +2304,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="31" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2500,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762865AC-13CA-4EC7-88AB-2DFC0996DA3B}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
@@ -2514,30 +2343,31 @@
     <col min="10" max="10" width="17.140625" customWidth="1"/>
     <col min="11" max="11" width="16.7109375" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17"/>
-      <c r="I1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="I1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="17"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="18"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -2574,7 +2404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
@@ -2616,7 +2446,7 @@
         <v>0.73400738868364701</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -2658,7 +2488,7 @@
         <v>0.52113821138211303</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2700,7 +2530,7 @@
         <v>0.65955305013086296</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -2709,7 +2539,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2718,18 +2548,37 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="1" t="s">
         <v>3</v>
@@ -2749,8 +2598,32 @@
       <c r="G9" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.87567147815804802</v>
+      </c>
+      <c r="K9" s="23">
+        <f>G3</f>
+        <v>9.0312408140650335E-3</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.749473198588546</v>
+      </c>
+      <c r="M9" s="24">
+        <f>G4</f>
+        <v>-3.2738619497879595E-3</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0.84310593832299696</v>
+      </c>
+      <c r="O9" s="23">
+        <f>G5</f>
+        <v>1.3338552650321911E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>0</v>
       </c>
@@ -2773,8 +2646,32 @@
         <f>E10-M3</f>
         <v>6.7472993641579659E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.87338753670814095</v>
+      </c>
+      <c r="K10" s="23">
+        <f>G10</f>
+        <v>6.7472993641579659E-3</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0.74658869395711402</v>
+      </c>
+      <c r="M10" s="24">
+        <f>G11</f>
+        <v>-6.1583665812199317E-3</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0.84628444416553295</v>
+      </c>
+      <c r="O10" s="23">
+        <f>G12</f>
+        <v>1.6517058492857895E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -2797,8 +2694,32 @@
         <f t="shared" ref="G11:G12" si="0">E11-M4</f>
         <v>-6.1583665812199317E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.86060161408657299</v>
+      </c>
+      <c r="K11" s="24">
+        <f>G17</f>
+        <v>-6.0386232574100029E-3</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.74225319396051104</v>
+      </c>
+      <c r="M11" s="24">
+        <f>G18</f>
+        <v>-1.0493866577822919E-2</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0.82986953966633203</v>
+      </c>
+      <c r="O11" s="23">
+        <f>G19</f>
+        <v>1.0215399365698374E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -2822,7 +2743,7 @@
         <v>1.6517058492857895E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2831,7 +2752,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2840,18 +2761,18 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="1" t="s">
         <v>3</v>
@@ -2973,41 +2894,41 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="13"/>
-      <c r="I25" s="13" t="s">
+      <c r="G25" s="12"/>
+      <c r="I25" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="13"/>
-      <c r="L25" s="13" t="s">
+      <c r="J25" s="12"/>
+      <c r="L25" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M25" s="13"/>
+      <c r="M25" s="12"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -3124,12 +3045,12 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -3146,12 +3067,12 @@
       <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
@@ -3236,12 +3157,12 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
       <c r="F35" s="8" t="s">
         <v>2</v>
       </c>
@@ -3314,11 +3235,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A8:G8"/>
@@ -3327,9 +3243,14 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3341,7 +3262,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:G9">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3353,7 +3274,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:G16">
-    <cfRule type="colorScale" priority="7">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3365,23 +3286,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:G28">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G23">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G33:I35">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:N2">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -3392,18 +3327,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33:I35">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
-      <formula>0.01</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="K9">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
-      <formula>0.01</formula>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/results/llm/results_for_presentation_few-shot.xlsx
+++ b/src/results/llm/results_for_presentation_few-shot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\llm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DEF4BF-079E-454D-8AFF-7E1ABCF466A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E937E0-EA2F-4E6B-B30E-3396ADF48CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OG" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="35">
   <si>
     <t>human1</t>
   </si>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>F1 makro diff</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (zero-shot) without texts  1, 5, 7, 43, 57</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (two-shot) without texts 1, 5, 7, 43, 57</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (three-shot) without texts  1, 5, 7, 43, 57</t>
+  </si>
+  <si>
+    <t>gemma-26b-q4 OG results (four-shot) without texts  1, 5, 7, 43, 57</t>
   </si>
 </sst>
 </file>
@@ -287,18 +299,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -317,11 +319,21 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -767,23 +779,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18"/>
-      <c r="I1" s="16" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="18"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -949,23 +961,23 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
-      <c r="I8" s="16" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="I8" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="18"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1131,23 +1143,23 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="16" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="I15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="18"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="16"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -1313,35 +1325,35 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="20"/>
+      <c r="D25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="20"/>
+      <c r="F25" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="20"/>
+      <c r="I25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -1612,23 +1624,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18"/>
-      <c r="I1" s="16" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="18"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1808,15 +1820,15 @@
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
@@ -1926,15 +1938,15 @@
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -2058,37 +2070,37 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="20"/>
+      <c r="D25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="20"/>
+      <c r="F25" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="20"/>
+      <c r="I25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="20"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -2187,12 +2199,12 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -2256,16 +2268,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="7">
@@ -2349,23 +2361,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18"/>
-      <c r="I1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="18"/>
+      <c r="A1" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="I1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -2408,126 +2420,126 @@
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6">
-        <v>0.85885486018641799</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="4">
+        <v>0.86</v>
+      </c>
+      <c r="C3" s="4">
         <v>0.95982142857142805</v>
       </c>
-      <c r="D3" s="6">
-        <v>0.90653548840477804</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0.87567147815804802</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.75260901063184005</v>
+      <c r="D3" s="4">
+        <v>0.90717299578058996</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.87309869301224596</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.74751476806208195</v>
       </c>
       <c r="G3" s="6">
         <f>E3-M3</f>
-        <v>9.0312408140650335E-3</v>
+        <v>2.8025595582179541E-3</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="6">
-        <v>0.86164383561643798</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0.93601190476190399</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0.897289586305278</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0.86664023734398299</v>
-      </c>
-      <c r="N3" s="6">
-        <v>0.73400738868364701</v>
+      <c r="J3" s="4">
+        <v>0.865122615803814</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.94494047619047605</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.903271692745377</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.87029613345402801</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.74143785085562097</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
-        <v>0.66352624495289303</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="4">
+        <v>0.66621621621621596</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.93904761904761902</v>
       </c>
-      <c r="D4" s="6">
-        <v>0.77760252365930604</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.749473198588546</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.51684025429460301</v>
+      <c r="D4" s="4">
+        <v>0.77944664031620503</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.746939287404776</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.51212591546879005</v>
       </c>
       <c r="G4" s="6">
         <f>E4-M4</f>
-        <v>-3.2738619497879595E-3</v>
+        <v>-7.5922765857630026E-3</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="6">
-        <v>0.66849315068493098</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0.92952380952380897</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0.777689243027888</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0.75274706053833396</v>
-      </c>
-      <c r="N4" s="6">
-        <v>0.52113821138211303</v>
+      <c r="J4" s="4">
+        <v>0.673024523160762</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.94095238095238098</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.78474980142970596</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.754531563990539</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.52580002154099204</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
-        <v>0.88297872340425498</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.89972899728997202</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.89127516778523397</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.84310593832299696</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.68626411709544499</v>
+      <c r="B5" s="4">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.90450204638471998</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.89413351314902201</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.84364119662721204</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.68736266371550903</v>
       </c>
       <c r="G5" s="6">
         <f>E5-M5</f>
-        <v>1.3338552650321911E-2</v>
+        <v>1.0274000022335028E-2</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="6">
-        <v>0.88356164383561597</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0.87398373983739797</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0.87874659400544897</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0.82976738567267505</v>
-      </c>
-      <c r="N5" s="6">
-        <v>0.65955305013086296</v>
+      <c r="J5" s="4">
+        <v>0.884196185286103</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.88540245566166398</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0.88479890933878602</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.83336719660487701</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.66673468633842403</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2549,15 +2561,15 @@
       <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="21"/>
+      <c r="A8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
         <v>0</v>
@@ -2604,47 +2616,47 @@
       <c r="J9" s="6">
         <v>0.87567147815804802</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="12">
         <f>G3</f>
-        <v>9.0312408140650335E-3</v>
+        <v>2.8025595582179541E-3</v>
       </c>
       <c r="L9" s="6">
         <v>0.749473198588546</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="13">
         <f>G4</f>
-        <v>-3.2738619497879595E-3</v>
+        <v>-7.5922765857630026E-3</v>
       </c>
       <c r="N9" s="6">
         <v>0.84310593832299696</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="12">
         <f>G5</f>
-        <v>1.3338552650321911E-2</v>
+        <v>1.0274000022335028E-2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="6">
-        <v>0.86118598382749301</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B10" s="4">
+        <v>0.86468200270635998</v>
+      </c>
+      <c r="C10" s="4">
         <v>0.95089285714285698</v>
       </c>
-      <c r="D10" s="6">
-        <v>0.90381895332390305</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.87338753670814095</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.74778432827079999</v>
+      <c r="D10" s="4">
+        <v>0.90574060949681001</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.872846237359717</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.746662362046846</v>
       </c>
       <c r="G10" s="6">
         <f>E10-M3</f>
-        <v>6.7472993641579659E-3</v>
+        <v>2.550103905688994E-3</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>17</v>
@@ -2652,47 +2664,47 @@
       <c r="J10" s="6">
         <v>0.87338753670814095</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="12">
         <f>G10</f>
-        <v>6.7472993641579659E-3</v>
+        <v>2.550103905688994E-3</v>
       </c>
       <c r="L10" s="6">
         <v>0.74658869395711402</v>
       </c>
-      <c r="M10" s="24">
+      <c r="M10" s="13">
         <f>G11</f>
-        <v>-6.1583665812199317E-3</v>
+        <v>-1.042614197094005E-2</v>
       </c>
       <c r="N10" s="6">
         <v>0.84628444416553295</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="12">
         <f>G12</f>
-        <v>1.6517058492857895E-2</v>
+        <v>1.0673045243206003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="6">
-        <v>0.66392318244170101</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="4">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="C11" s="4">
         <v>0.92190476190476101</v>
       </c>
-      <c r="D11" s="6">
-        <v>0.77192982456140302</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.74658869395711402</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.50905723449428497</v>
+      <c r="D11" s="4">
+        <v>0.77378097521982403</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.74410542201959895</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.50436279725217903</v>
       </c>
       <c r="G11" s="6">
         <f t="shared" ref="G11:G12" si="0">E11-M4</f>
-        <v>-6.1583665812199317E-3</v>
+        <v>-1.042614197094005E-2</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -2700,47 +2712,47 @@
       <c r="J11" s="6">
         <v>0.86060161408657299</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="13">
         <f>G17</f>
-        <v>-6.0386232574100029E-3</v>
+        <v>-1.1581968422416988E-2</v>
       </c>
       <c r="L11" s="6">
         <v>0.74225319396051104</v>
       </c>
-      <c r="M11" s="24">
+      <c r="M11" s="13">
         <f>G18</f>
-        <v>-1.0493866577822919E-2</v>
+        <v>-1.4663007175688025E-2</v>
       </c>
       <c r="N11" s="6">
         <v>0.82986953966633203</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="12">
         <f>G19</f>
-        <v>1.0215399365698374E-4</v>
+        <v>-4.362690110535028E-3</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="6">
-        <v>0.88651535380507296</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.89972899728997202</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.89307330195023504</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.84628444416553295</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.69260043143799099</v>
+      <c r="B12" s="4">
+        <v>0.886058981233244</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.90177353342428301</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.89384719405003299</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.84404024184808302</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.688127189570511</v>
       </c>
       <c r="G12" s="6">
         <f t="shared" si="0"/>
-        <v>1.6517058492857895E-2</v>
+        <v>1.0673045243206003E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2762,15 +2774,15 @@
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="A15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
@@ -2797,72 +2809,72 @@
       <c r="A17" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="6">
-        <v>0.85365853658536495</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B17" s="4">
+        <v>0.85597826086956497</v>
+      </c>
+      <c r="C17" s="4">
         <v>0.9375</v>
       </c>
-      <c r="D17" s="6">
-        <v>0.89361702127659504</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.86060161408657299</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.72218972979295804</v>
+      <c r="D17" s="4">
+        <v>0.89488636363636298</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0.85871416503161102</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.71841054746904098</v>
       </c>
       <c r="G17" s="6">
         <f>E17-M3</f>
-        <v>-6.0386232574100029E-3</v>
+        <v>-1.1581968422416988E-2</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="6">
-        <v>0.66524822695035402</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="4">
+        <v>0.66809116809116798</v>
+      </c>
+      <c r="C18" s="4">
         <v>0.89333333333333298</v>
       </c>
-      <c r="D18" s="6">
-        <v>0.76260162601626003</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.74225319396051104</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0.49712213913437497</v>
+      <c r="D18" s="4">
+        <v>0.76446617766911096</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0.73986855681485098</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.492503528534526</v>
       </c>
       <c r="G18" s="6">
         <f t="shared" ref="G18:G19" si="1">E18-M4</f>
-        <v>-1.0493866577822919E-2</v>
+        <v>-1.4663007175688025E-2</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="6">
-        <v>0.87956698240866005</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.88075880758807501</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.88016249153689896</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.82986953966633203</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0.65973936622283302</v>
+      <c r="B19" s="4">
+        <v>0.87940379403794</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.88540245566166398</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.88239292997960495</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.82900450649434199</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.65801655136902304</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="1"/>
-        <v>1.0215399365698374E-4</v>
+        <v>-4.362690110535028E-3</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -2894,41 +2906,41 @@
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
+      <c r="C25" s="20"/>
+      <c r="D25" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
+      <c r="E25" s="20"/>
+      <c r="F25" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="I25" s="12" t="s">
+      <c r="G25" s="20"/>
+      <c r="I25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="12"/>
-      <c r="L25" s="12" t="s">
+      <c r="J25" s="20"/>
+      <c r="L25" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="M25" s="12"/>
+      <c r="M25" s="20"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
@@ -3045,12 +3057,12 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
@@ -3067,12 +3079,12 @@
       <c r="D31" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
@@ -3157,12 +3169,12 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
       <c r="F35" s="8" t="s">
         <v>2</v>
       </c>
@@ -3235,6 +3247,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="A8:G8"/>
@@ -3243,11 +3260,6 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="A30:D30"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:G2">
     <cfRule type="colorScale" priority="13">
